--- a/louvain_baseline_experiments/louvain_Baseline_polbooks_normalized/louvain_Baseline_polbooks_normalized_results.xlsx
+++ b/louvain_baseline_experiments/louvain_Baseline_polbooks_normalized/louvain_Baseline_polbooks_normalized_results.xlsx
@@ -550,13 +550,13 @@
         <v>0.5266195669499848</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002413000000160537</v>
+        <v>0.002540400004363619</v>
       </c>
       <c r="O2" t="n">
-        <v>0.008969800000159012</v>
+        <v>0.01076330000068992</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1133632999999463</v>
+        <v>0.08939740000641905</v>
       </c>
     </row>
   </sheetData>
